--- a/SGC-CKN/Excel/33477562-2c66-4d1d-a4ee-85b893b7edc6_Thanh_Hoá_P2-12_D800_08-04-2026.xlsx
+++ b/SGC-CKN/Excel/33477562-2c66-4d1d-a4ee-85b893b7edc6_Thanh_Hoá_P2-12_D800_08-04-2026.xlsx
@@ -345,12 +345,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -514,17 +514,17 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1253,53 +1253,53 @@
         <v>-10.28</v>
       </c>
       <c r="G14" s="15">
-        <v>-12.08</v>
+        <v>-19.08</v>
       </c>
       <c r="H14" s="15">
         <v>0.83</v>
       </c>
       <c r="I14" s="15">
-        <v>1.8</v>
-      </c>
-      <c r="J14" s="8">
-        <v>2.16</v>
+        <v>8.8</v>
+      </c>
+      <c r="J14" s="18">
+        <v>10.56</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="18">
-        <v>-12.08</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="F15" s="19">
+        <v>-19.08</v>
+      </c>
+      <c r="G15" s="19">
         <v>-24.28</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="19">
         <v>1</v>
       </c>
-      <c r="I15" s="18">
-        <v>12.2</v>
-      </c>
-      <c r="J15" s="21">
-        <v>12.2</v>
-      </c>
-      <c r="K15" s="19" t="s">
+      <c r="I15" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="J15" s="18">
+        <v>5.2</v>
+      </c>
+      <c r="K15" s="20" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       <c r="I17" s="25">
         <v>9.66</v>
       </c>
-      <c r="J17" s="21">
+      <c r="J17" s="18">
         <v>6.37</v>
       </c>
       <c r="K17" s="26" t="s">
@@ -1647,45 +1647,45 @@
         <v>-10.28</v>
       </c>
       <c r="F5" s="15">
-        <v>-12.08</v>
+        <v>-19.08</v>
       </c>
       <c r="G5" s="15">
         <v>0.83</v>
       </c>
       <c r="H5" s="15">
-        <v>1.8</v>
-      </c>
-      <c r="I5" s="8">
-        <v>2.16</v>
+        <v>8.8</v>
+      </c>
+      <c r="I5" s="18">
+        <v>10.56</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <v>1</v>
       </c>
-      <c r="E6" s="18">
-        <v>-12.08</v>
-      </c>
-      <c r="F6" s="18">
+      <c r="E6" s="19">
+        <v>-19.08</v>
+      </c>
+      <c r="F6" s="19">
         <v>-24.28</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <v>1</v>
       </c>
-      <c r="H6" s="18">
-        <v>12.2</v>
-      </c>
-      <c r="I6" s="21">
-        <v>12.2</v>
+      <c r="H6" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="I6" s="18">
+        <v>5.2</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
       <c r="H8" s="25">
         <v>9.66</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="18">
         <v>6.37</v>
       </c>
     </row>
